--- a/db/A7XLK-2102-Population-01.xlsx
+++ b/db/A7XLK-2102-Population-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFFD7AB-F46E-D342-9360-D054D7554EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265AEC0E-1842-FE48-BD22-D67567444AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3040" yWindow="2220" windowWidth="23260" windowHeight="15780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="20" r:id="rId4"/>
+    <pivotCache cacheId="17" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="55">
   <si>
     <t>里別</t>
   </si>
@@ -196,6 +197,24 @@
   </si>
   <si>
     <t>加總 - 戶數</t>
+  </si>
+  <si>
+    <t>A7重劃區</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A7</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -365,15 +384,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -385,6 +395,15 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -518,8 +537,7 @@
           <a:sp3d/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1034,19 +1052,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1094,7 +1100,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -1102,19 +1108,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1575,6 +1569,1181 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-2102-Population-01.xlsx]工作表3!樞紐分析表3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/04</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" baseline="0">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>重劃區佔龜山人口</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="threePt" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="matte"/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="threePt" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="matte"/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0.11004879483443178"/>
+              <c:y val="0.22506689712566422"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="60"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$C$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-99B3-0F4F-8CBE-E416FD8D1E1B}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.11004879483443178"/>
+                  <c:y val="0.22506689712566422"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-99B3-0F4F-8CBE-E416FD8D1E1B}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$B$56:$B$58</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>其他</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>A7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$C$56:$C$58</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ </c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>135004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33053</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-99B3-0F4F-8CBE-E416FD8D1E1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:pattFill prst="dkDnDiag">
+      <a:fgClr>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="lt1"/>
+      </a:bgClr>
+    </a:pattFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-2102-Population-01.xlsx]工作表3!樞紐分析表4</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1600">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>2022/04</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1600" baseline="0">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t> A7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="1600" baseline="0">
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>人口及戶數</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600">
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$C$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>加總 - 戶數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$B$78:$B$80</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>A7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>其他</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$C$78:$C$80</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ </c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15882</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53655</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6ADF-C746-BDD5-6223732CCF3B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表3!$D$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>加總 - 總人口數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表3!$B$78:$B$80</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>A7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>其他</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表3!$D$78:$D$80</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ </c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>33053</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6ADF-C746-BDD5-6223732CCF3B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-25"/>
+        <c:axId val="741444160"/>
+        <c:axId val="741445808"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="741444160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741445808"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="741445808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="741444160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:ea typeface="Kaiti TC" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1655,6 +2824,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="264">
   <cs:axisTitle>
@@ -2257,6 +3506,1040 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="261">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="25000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="matte"/>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="78000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2833,15 +5116,87 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24C57AD3-0727-0200-C849-A3656D573C32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="圖表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD2BEB6C-FE9B-146E-7060-8BF19831C3C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44683.856764814816" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="32" xr:uid="{31DB7F1D-79A9-1C47-89CD-2BE2E112338C}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44683.922523611109" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="32" xr:uid="{4BBDDF00-FCAE-7942-A328-F426F7011483}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G33" sheet="工作表2"/>
+    <worksheetSource ref="A1:H33" sheet="工作表2"/>
   </cacheSource>
-  <cacheFields count="7">
+  <cacheFields count="8">
     <cacheField name="里別" numFmtId="0">
       <sharedItems/>
     </cacheField>
@@ -2927,6 +5282,50 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="733" maxValue="5708"/>
     </cacheField>
     <cacheField name="區域" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="A7重劃區" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="其他"/>
+        <s v="A7"/>
+        <m u="1"/>
+        <s v="Y" u="1"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="44683.922523726855" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="32" xr:uid="{31DB7F1D-79A9-1C47-89CD-2BE2E112338C}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G33" sheet="工作表2"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="里別" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="鄰數" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="14" maxValue="42"/>
+    </cacheField>
+    <cacheField name="戶數" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="628" maxValue="4862"/>
+    </cacheField>
+    <cacheField name="總人口數" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1466" maxValue="11241"/>
+    </cacheField>
+    <cacheField name="男人口數" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="733" maxValue="5533"/>
+    </cacheField>
+    <cacheField name="女人口數" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="733" maxValue="5708"/>
+    </cacheField>
+    <cacheField name="區域" numFmtId="0">
       <sharedItems count="2">
         <s v="上龜山"/>
         <s v="下龜山"/>
@@ -2950,6 +5349,7 @@
     <x v="0"/>
     <n v="2421"/>
     <n v="2356"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -2959,7 +5359,8 @@
     <x v="1"/>
     <n v="3874"/>
     <n v="3949"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="兔坑里"/>
@@ -2968,7 +5369,8 @@
     <x v="2"/>
     <n v="2702"/>
     <n v="2465"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="大同里"/>
@@ -2977,7 +5379,8 @@
     <x v="3"/>
     <n v="3458"/>
     <n v="3507"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="山福里"/>
@@ -2986,7 +5389,8 @@
     <x v="4"/>
     <n v="1885"/>
     <n v="1930"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="山頂里"/>
@@ -2995,7 +5399,8 @@
     <x v="5"/>
     <n v="3359"/>
     <n v="3026"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="陸光里"/>
@@ -3004,7 +5409,8 @@
     <x v="6"/>
     <n v="1970"/>
     <n v="2097"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="精忠里"/>
@@ -3013,7 +5419,8 @@
     <x v="7"/>
     <n v="3165"/>
     <n v="3329"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="公西里"/>
@@ -3022,6 +5429,7 @@
     <x v="8"/>
     <n v="733"/>
     <n v="733"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3031,7 +5439,8 @@
     <x v="9"/>
     <n v="4306"/>
     <n v="4416"/>
-    <x v="0"/>
+    <s v="上龜山"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="南上里"/>
@@ -3040,6 +5449,7 @@
     <x v="10"/>
     <n v="1123"/>
     <n v="1105"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3049,6 +5459,7 @@
     <x v="11"/>
     <n v="1186"/>
     <n v="1104"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3058,7 +5469,8 @@
     <x v="12"/>
     <n v="2695"/>
     <n v="2801"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="山德里"/>
@@ -3067,7 +5479,8 @@
     <x v="13"/>
     <n v="2657"/>
     <n v="2740"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="新路里"/>
@@ -3076,7 +5489,8 @@
     <x v="14"/>
     <n v="3042"/>
     <n v="3108"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="嶺頂里"/>
@@ -3085,7 +5499,8 @@
     <x v="15"/>
     <n v="2413"/>
     <n v="2238"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="龍壽里"/>
@@ -3094,7 +5509,8 @@
     <x v="16"/>
     <n v="1030"/>
     <n v="965"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="舊路里"/>
@@ -3103,6 +5519,7 @@
     <x v="17"/>
     <n v="1491"/>
     <n v="1471"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3112,6 +5529,7 @@
     <x v="18"/>
     <n v="2567"/>
     <n v="2398"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3121,7 +5539,8 @@
     <x v="19"/>
     <n v="4171"/>
     <n v="4538"/>
-    <x v="0"/>
+    <s v="上龜山"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="南美里"/>
@@ -3130,6 +5549,7 @@
     <x v="20"/>
     <n v="1477"/>
     <n v="1476"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3139,7 +5559,8 @@
     <x v="21"/>
     <n v="3127"/>
     <n v="3087"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="福源里"/>
@@ -3148,7 +5569,8 @@
     <x v="22"/>
     <n v="1163"/>
     <n v="1073"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="龍華里"/>
@@ -3157,7 +5579,8 @@
     <x v="23"/>
     <n v="1904"/>
     <n v="1927"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="迴龍里"/>
@@ -3166,7 +5589,8 @@
     <x v="24"/>
     <n v="3355"/>
     <n v="3475"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="新嶺里"/>
@@ -3175,7 +5599,8 @@
     <x v="25"/>
     <n v="2324"/>
     <n v="2177"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="大湖里"/>
@@ -3184,6 +5609,7 @@
     <x v="26"/>
     <n v="3047"/>
     <n v="3378"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3193,6 +5619,7 @@
     <x v="27"/>
     <n v="5533"/>
     <n v="5708"/>
+    <s v="上龜山"/>
     <x v="0"/>
   </r>
   <r>
@@ -3202,7 +5629,8 @@
     <x v="28"/>
     <n v="2614"/>
     <n v="3319"/>
-    <x v="0"/>
+    <s v="上龜山"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="★新興里"/>
@@ -3211,7 +5639,8 @@
     <x v="29"/>
     <n v="1972"/>
     <n v="1491"/>
-    <x v="1"/>
+    <s v="下龜山"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="文青里"/>
@@ -3220,7 +5649,8 @@
     <x v="30"/>
     <n v="4543"/>
     <n v="5146"/>
-    <x v="0"/>
+    <s v="上龜山"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="楓福里"/>
@@ -3229,15 +5659,309 @@
     <x v="31"/>
     <n v="2056"/>
     <n v="2161"/>
+    <s v="下龜山"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="32">
+  <r>
+    <s v="楓樹里"/>
+    <n v="25"/>
+    <n v="1717"/>
+    <n v="4777"/>
+    <n v="2421"/>
+    <n v="2356"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="龜山里"/>
+    <n v="39"/>
+    <n v="2963"/>
+    <n v="7823"/>
+    <n v="3874"/>
+    <n v="3949"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="兔坑里"/>
+    <n v="29"/>
+    <n v="1924"/>
+    <n v="5167"/>
+    <n v="2702"/>
+    <n v="2465"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="大同里"/>
+    <n v="34"/>
+    <n v="2650"/>
+    <n v="6965"/>
+    <n v="3458"/>
+    <n v="3507"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="山福里"/>
+    <n v="19"/>
+    <n v="1455"/>
+    <n v="3815"/>
+    <n v="1885"/>
+    <n v="1930"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="山頂里"/>
+    <n v="31"/>
+    <n v="2572"/>
+    <n v="6385"/>
+    <n v="3359"/>
+    <n v="3026"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="陸光里"/>
+    <n v="30"/>
+    <n v="1711"/>
+    <n v="4067"/>
+    <n v="1970"/>
+    <n v="2097"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="精忠里"/>
+    <n v="35"/>
+    <n v="2627"/>
+    <n v="6494"/>
+    <n v="3165"/>
+    <n v="3329"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="公西里"/>
+    <n v="14"/>
+    <n v="628"/>
+    <n v="1466"/>
+    <n v="733"/>
+    <n v="733"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="樂善里"/>
+    <n v="28"/>
+    <n v="4199"/>
+    <n v="8722"/>
+    <n v="4306"/>
+    <n v="4416"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="南上里"/>
+    <n v="15"/>
+    <n v="956"/>
+    <n v="2228"/>
+    <n v="1123"/>
+    <n v="1105"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="大坑里"/>
+    <n v="18"/>
+    <n v="908"/>
+    <n v="2290"/>
+    <n v="1186"/>
+    <n v="1104"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="中興里"/>
+    <n v="32"/>
+    <n v="2200"/>
+    <n v="5496"/>
+    <n v="2695"/>
+    <n v="2801"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="山德里"/>
+    <n v="34"/>
+    <n v="2150"/>
+    <n v="5397"/>
+    <n v="2657"/>
+    <n v="2740"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="新路里"/>
+    <n v="42"/>
+    <n v="2371"/>
+    <n v="6150"/>
+    <n v="3042"/>
+    <n v="3108"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="嶺頂里"/>
+    <n v="30"/>
+    <n v="1673"/>
+    <n v="4651"/>
+    <n v="2413"/>
+    <n v="2238"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="龍壽里"/>
+    <n v="17"/>
+    <n v="786"/>
+    <n v="1995"/>
+    <n v="1030"/>
+    <n v="965"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="舊路里"/>
+    <n v="17"/>
+    <n v="1232"/>
+    <n v="2962"/>
+    <n v="1491"/>
+    <n v="1471"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="大崗里"/>
+    <n v="26"/>
+    <n v="1898"/>
+    <n v="4965"/>
+    <n v="2567"/>
+    <n v="2398"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="文化里"/>
+    <n v="33"/>
+    <n v="4034"/>
+    <n v="8709"/>
+    <n v="4171"/>
+    <n v="4538"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="南美里"/>
+    <n v="14"/>
+    <n v="1095"/>
+    <n v="2953"/>
+    <n v="1477"/>
+    <n v="1476"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="幸福里"/>
+    <n v="27"/>
+    <n v="2378"/>
+    <n v="6214"/>
+    <n v="3127"/>
+    <n v="3087"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="福源里"/>
+    <n v="23"/>
+    <n v="802"/>
+    <n v="2236"/>
+    <n v="1163"/>
+    <n v="1073"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="龍華里"/>
+    <n v="18"/>
+    <n v="1594"/>
+    <n v="3831"/>
+    <n v="1904"/>
+    <n v="1927"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="迴龍里"/>
+    <n v="35"/>
+    <n v="2848"/>
+    <n v="6830"/>
+    <n v="3355"/>
+    <n v="3475"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="新嶺里"/>
+    <n v="25"/>
+    <n v="1680"/>
+    <n v="4501"/>
+    <n v="2324"/>
+    <n v="2177"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="大湖里"/>
+    <n v="23"/>
+    <n v="3063"/>
+    <n v="6425"/>
+    <n v="3047"/>
+    <n v="3378"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="大華里"/>
+    <n v="37"/>
+    <n v="4440"/>
+    <n v="11241"/>
+    <n v="5533"/>
+    <n v="5708"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="長庚里"/>
+    <n v="27"/>
+    <n v="2787"/>
+    <n v="5933"/>
+    <n v="2614"/>
+    <n v="3319"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="★新興里"/>
+    <n v="20"/>
+    <n v="1861"/>
+    <n v="3463"/>
+    <n v="1972"/>
+    <n v="1491"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="文青里"/>
+    <n v="41"/>
+    <n v="4862"/>
+    <n v="9689"/>
+    <n v="4543"/>
+    <n v="5146"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="楓福里"/>
+    <n v="19"/>
+    <n v="1473"/>
+    <n v="4217"/>
+    <n v="2056"/>
+    <n v="2161"/>
     <x v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A3D1372F-049F-2E42-A8CC-40EDE5E095FD}" name="樞紐分析表2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="B34:D37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B24877BF-B546-5E43-8FFC-CCD947E1FCB5}" name="樞紐分析表4" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="B77:D80" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0">
@@ -3316,23 +6040,26 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="3">
+      <items count="5">
+        <item x="1"/>
+        <item m="1" x="3"/>
         <item x="0"/>
-        <item x="1"/>
+        <item m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="6"/>
+    <field x="7"/>
   </rowFields>
   <rowItems count="3">
     <i>
       <x/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -3350,8 +6077,8 @@
     </i>
   </colItems>
   <dataFields count="2">
+    <dataField name="加總 - 戶數" fld="2" baseField="0" baseItem="0" numFmtId="176"/>
     <dataField name="加總 - 總人口數" fld="3" baseField="0" baseItem="0" numFmtId="176"/>
-    <dataField name="加總 - 戶數" fld="2" baseField="0" baseItem="0" numFmtId="176"/>
   </dataFields>
   <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
@@ -3386,49 +6113,89 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10B91744-BD95-9F41-951D-B6A16C2C7F80}" name="樞紐分析表1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{116AEF3D-4570-A745-B1E7-8959194332E4}" name="樞紐分析表3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="B55:C58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item m="1" x="3"/>
+        <item m="1" x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="加總 - 總人口數" fld="3" baseField="0" baseItem="0" numFmtId="176"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10B91744-BD95-9F41-951D-B6A16C2C7F80}" name="樞紐分析表1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="33">
-        <item x="8"/>
-        <item x="16"/>
-        <item x="10"/>
-        <item x="22"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="17"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="23"/>
-        <item x="6"/>
-        <item x="31"/>
-        <item x="25"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="28"/>
-        <item x="14"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="26"/>
-        <item x="7"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="9"/>
-        <item x="30"/>
-        <item x="27"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -3488,6 +6255,85 @@
             <x v="0"/>
           </reference>
           <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A3D1372F-049F-2E42-A8CC-40EDE5E095FD}" name="樞紐分析表2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="B34:D37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="加總 - 總人口數" fld="3" baseField="0" baseItem="0" numFmtId="176"/>
+    <dataField name="加總 - 戶數" fld="2" baseField="0" baseItem="0" numFmtId="176"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
@@ -3776,24 +6622,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.5" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" ht="37" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="7" t="s">
@@ -4493,16 +7339,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9A2B5D-E341-5B42-A773-FFAB977326DA}">
-  <dimension ref="A3:D37"/>
+  <dimension ref="A3:D80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>46</v>
       </c>
       <c r="B3" t="s">
@@ -4510,31 +7356,31 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="12">
         <v>72360</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="12">
         <v>95697</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="12">
         <v>168057</v>
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C34" t="s">
@@ -4545,54 +7391,130 @@
       </c>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="12">
         <v>72360</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="12">
         <v>31819</v>
       </c>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="12">
         <v>95697</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="12">
         <v>37718</v>
       </c>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="12">
         <v>168057</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="12">
         <v>69537</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3">
+      <c r="B55" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="12">
+        <v>135004</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" s="12">
+        <v>33053</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="12">
+        <v>168057</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D77" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" s="12">
+        <v>15882</v>
+      </c>
+      <c r="D78" s="12">
+        <v>33053</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="12">
+        <v>53655</v>
+      </c>
+      <c r="D79" s="12">
+        <v>135004</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="12">
+        <v>69537</v>
+      </c>
+      <c r="D80" s="12">
+        <v>168057</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9A6596-8205-564B-860A-D722F022E56E}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="6" width="11.1640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21">
+    <row r="1" spans="1:8">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4611,11 +7533,14 @@
       <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="22">
+      <c r="H1" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="22">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -4637,8 +7562,11 @@
       <c r="G2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="22">
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="22">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -4660,8 +7588,11 @@
       <c r="G3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="22">
+      <c r="H3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="22">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -4683,8 +7614,11 @@
       <c r="G4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="22">
+      <c r="H4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="22">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -4706,8 +7640,11 @@
       <c r="G5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="22">
+      <c r="H5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="22">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -4729,8 +7666,11 @@
       <c r="G6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="22">
+      <c r="H6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="22">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -4752,8 +7692,11 @@
       <c r="G7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="22">
+      <c r="H7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="22">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -4775,8 +7718,11 @@
       <c r="G8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="22">
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="22">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -4798,8 +7744,11 @@
       <c r="G9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="22">
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="22">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -4821,8 +7770,11 @@
       <c r="G10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="22">
+      <c r="H10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="22">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -4844,8 +7796,11 @@
       <c r="G11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="22">
+      <c r="H11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="22">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -4867,8 +7822,11 @@
       <c r="G12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="22">
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="22">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -4890,8 +7848,11 @@
       <c r="G13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="22">
+      <c r="H13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="22">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -4913,8 +7874,11 @@
       <c r="G14" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="22">
+      <c r="H14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="22">
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
@@ -4936,8 +7900,11 @@
       <c r="G15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="22">
+      <c r="H15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="22">
       <c r="A16" s="3" t="s">
         <v>20</v>
       </c>
@@ -4959,8 +7926,11 @@
       <c r="G16" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="22">
+      <c r="H16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="22">
       <c r="A17" s="3" t="s">
         <v>21</v>
       </c>
@@ -4982,8 +7952,11 @@
       <c r="G17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="22">
+      <c r="H17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="22">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
@@ -5005,8 +7978,11 @@
       <c r="G18" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="22">
+      <c r="H18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="22">
       <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
@@ -5028,8 +8004,11 @@
       <c r="G19" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="22">
+      <c r="H19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="22">
       <c r="A20" s="3" t="s">
         <v>24</v>
       </c>
@@ -5051,8 +8030,11 @@
       <c r="G20" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="22">
+      <c r="H20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="22">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
@@ -5074,8 +8056,11 @@
       <c r="G21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="22">
+      <c r="H21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="22">
       <c r="A22" s="3" t="s">
         <v>26</v>
       </c>
@@ -5097,8 +8082,11 @@
       <c r="G22" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="22">
+      <c r="H22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="22">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
@@ -5120,8 +8108,11 @@
       <c r="G23" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="22">
+      <c r="H23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="22">
       <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
@@ -5143,8 +8134,11 @@
       <c r="G24" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="22">
+      <c r="H24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="22">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
@@ -5166,8 +8160,11 @@
       <c r="G25" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="22">
+      <c r="H25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="22">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
@@ -5189,8 +8186,11 @@
       <c r="G26" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="22">
+      <c r="H26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="22">
       <c r="A27" s="3" t="s">
         <v>31</v>
       </c>
@@ -5212,8 +8212,11 @@
       <c r="G27" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="22">
+      <c r="H27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="22">
       <c r="A28" s="3" t="s">
         <v>32</v>
       </c>
@@ -5235,8 +8238,11 @@
       <c r="G28" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="22">
+      <c r="H28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="22">
       <c r="A29" s="3" t="s">
         <v>33</v>
       </c>
@@ -5258,8 +8264,11 @@
       <c r="G29" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="22">
+      <c r="H29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="22">
       <c r="A30" s="3" t="s">
         <v>34</v>
       </c>
@@ -5281,8 +8290,11 @@
       <c r="G30" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="22">
+      <c r="H30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="22">
       <c r="A31" s="3" t="s">
         <v>36</v>
       </c>
@@ -5304,8 +8316,11 @@
       <c r="G31" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="22">
+      <c r="H31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="22">
       <c r="A32" s="4" t="s">
         <v>37</v>
       </c>
@@ -5327,8 +8342,11 @@
       <c r="G32" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="22">
+      <c r="H32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="22">
       <c r="A33" s="4" t="s">
         <v>38</v>
       </c>
@@ -5350,9 +8368,10 @@
       <c r="G33" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="21"/>
-    <row r="35" spans="1:7" ht="21"/>
+      <c r="H33" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
